--- a/reports/pdf_rolling5_20260907.xlsx
+++ b/reports/pdf_rolling5_20260907.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,314억   ·   현금 44억(1.0%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 13종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억   ·   현금 22억(0.5%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 13종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>116</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>442516800</v>
+        <v>441649120</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-98</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-6657336000</v>
+        <v>-6644282400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>109</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1304141400</v>
+        <v>1301584260</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-72</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-5272992000</v>
+        <v>-5262652800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>45</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2216970000</v>
+        <v>2212623000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-26</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1636284000</v>
+        <v>-1633075600</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1591506000</v>
+        <v>1588385400</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-24</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-880056000</v>
+        <v>-878330400</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1315800000</v>
+        <v>1313220000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-14</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1683612000</v>
+        <v>-1680310800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>449116200</v>
+        <v>448235580</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-12</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-581400000</v>
+        <v>-580260000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>29</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2437392000</v>
+        <v>2432612800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-10</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1032240000</v>
+        <v>-1030216000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>3672000000</v>
+        <v>3664800000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2648430000</v>
+        <v>-2643237000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1645056000</v>
+        <v>1641830400</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-4</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1242360000</v>
+        <v>-1239924000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>836349000</v>
+        <v>834709100</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-3</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-449208000</v>
+        <v>-448327200</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>5874180000</v>
+        <v>5862662000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1238688000</v>
+        <v>1236259200</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>928200000</v>
+        <v>926380000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,530억   ·   현금 89억(2.4%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 4종목  /  매도 5종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,620억   ·   현금 44억(1.2%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1475,7 +1475,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,410억   ·   현금 59억(2.3%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 7종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,506억   ·   현금 29억(1.2%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>로보티즈  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2180178000</v>
+        <v>-1322521200</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.59%→4.34%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>119→106</t>
         </is>
       </c>
     </row>
@@ -1877,30 +1877,30 @@
       <c r="E39" s="17" t="n"/>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>로보티즈  (편출)</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1322521200</v>
+        <v>-2180178000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>4.59%→4.34%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>119→106</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,990억   ·   현금 44억(2.1%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 5종목  /  매도 8종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,030억   ·   현금 22억(1.1%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 5종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -1996,7 +1996,7 @@
         <v>218</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>2053298400</v>
+        <v>2047150800</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>-285</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-8081631000</v>
+        <v>-8057434500</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>133</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>4086824000</v>
+        <v>4074588000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>-123</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-2021234400</v>
+        <v>-2015182800</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>86</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>2050893600</v>
+        <v>2044753200</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>-119</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-321545140</v>
+        <v>-320582430</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>52</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2657304000</v>
+        <v>2649348000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>-80</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-626584000</v>
+        <v>-624708000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>18</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1130857200</v>
+        <v>1127471400</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>-60</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-602202000</v>
+        <v>-600399000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>-43</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-310219200</v>
+        <v>-309290400</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>-17</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-143369500</v>
+        <v>-142940250</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>-5</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-26018600</v>
+        <v>-25940700</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 257억   ·   현금 3억(1.3%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 13종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 267억   ·   현금 2억(0.6%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 13종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>
@@ -2389,11 +2389,11 @@
         <v>89</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>115753400</v>
+        <v>121609600</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.46%</t>
+          <t>2.03%→2.48%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2410,11 +2410,11 @@
         <v>-386</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-272902000</v>
+        <v>-272091400</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>8.58%→7.50%</t>
+          <t>8.24%→7.20%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2433,11 +2433,11 @@
         <v>58</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>134792000</v>
+        <v>136619000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>6.79%→7.30%</t>
+          <t>6.63%→7.13%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2454,11 +2454,11 @@
         <v>-93</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-63081900</v>
+        <v>-66271800</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.81%</t>
+          <t>1.07%→0.82%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2477,11 +2477,11 @@
         <v>47</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>51126600</v>
+        <v>56686700</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>3.32%→3.51%</t>
+          <t>3.54%→3.75%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2498,11 +2498,11 @@
         <v>-84</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-121716000</v>
+        <v>-125538000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>5.65%→5.16%</t>
+          <t>5.61%→5.12%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2521,11 +2521,11 @@
         <v>41</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>142208500</v>
+        <v>143213000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>0.79%→1.35%</t>
+          <t>0.77%→1.30%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2542,11 +2542,11 @@
         <v>-49</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-136171000</v>
+        <v>-136514000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>3.13%→2.59%</t>
+          <t>3.02%→2.50%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2565,11 +2565,11 @@
         <v>30</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>51030000</v>
+        <v>52710000</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>2.21%→2.41%</t>
+          <t>2.20%→2.39%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2586,11 +2586,11 @@
         <v>-31</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-26604200</v>
+        <v>-26257000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.58%</t>
+          <t>2.56%→2.45%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2609,11 +2609,11 @@
         <v>25</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>60200000</v>
+        <v>70262500</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>3.15%→3.38%</t>
+          <t>3.54%→3.80%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2630,11 +2630,11 @@
         <v>-25</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-99225000</v>
+        <v>-103950000</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>1.89%→1.49%</t>
+          <t>1.90%→1.51%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2653,11 +2653,11 @@
         <v>21</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>76293000</v>
+        <v>77616000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.74%→3.03%</t>
+          <t>2.68%→2.97%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2674,11 +2674,11 @@
         <v>-15</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-33285000</v>
+        <v>-33390000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.29%</t>
+          <t>0.40%→0.28%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2697,11 +2697,11 @@
         <v>21</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>71295000</v>
+        <v>70560000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>1.05%→1.33%</t>
+          <t>1.00%→1.27%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2718,11 +2718,11 @@
         <v>-10</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-35140000</v>
+        <v>-35560000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.31%</t>
+          <t>1.41%→1.27%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2741,11 +2741,11 @@
         <v>15</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>34387500</v>
+        <v>37747500</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>1.08%→1.21%</t>
+          <t>1.14%→1.28%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -2762,11 +2762,11 @@
         <v>-5</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-46970000</v>
+        <v>-47075000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>0.41%→0.22%</t>
+          <t>0.39%→0.21%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2785,11 +2785,11 @@
         <v>14</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>67228000</v>
+        <v>73304000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.92%→1.19%</t>
+          <t>0.97%→1.24%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -2806,7 +2806,7 @@
         <v>-3</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-80010000</v>
+        <v>-81165000</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2829,11 +2829,11 @@
         <v>11</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>23908500</v>
+        <v>24640000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.14%→2.23%</t>
+          <t>2.13%→2.21%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2850,23 +2850,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>보로노이</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>87780000</v>
+        <v>32130000</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>0.80%→1.15%</t>
+          <t>0.08%→0.20%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>7→10</t>
+          <t>2→5</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>
@@ -2878,23 +2878,23 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>30912000</v>
+        <v>93030000</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.20%</t>
+          <t>0.82%→1.17%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>2→5</t>
+          <t>7→10</t>
         </is>
       </c>
       <c r="G68" s="17" t="n"/>
@@ -2906,7 +2906,7 @@
     <row r="70" ht="19" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 504억   ·   현금 9억(1.7%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 4종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 509억   ·   현금 4억(0.8%)      오늘 2026-09-07  vs  5일전 2026-08-31      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B70" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260907.xlsx
+++ b/reports/pdf_rolling5_20260907.xlsx
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>로보티즈  (편출)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1322521200</v>
+        <v>-2180178000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>4.59%→4.34%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>119→106</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1877,23 +1877,23 @@
       <c r="E39" s="17" t="n"/>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>로보티즈  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2180178000</v>
+        <v>-1322521200</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.59%→4.34%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>119→106</t>
         </is>
       </c>
     </row>
@@ -2646,23 +2646,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>77616000</v>
+        <v>70560000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.97%</t>
+          <t>1.00%→1.27%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>192→213</t>
+          <t>79→100</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -2690,23 +2690,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>70560000</v>
+        <v>77616000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.27%</t>
+          <t>2.68%→2.97%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>79→100</t>
+          <t>192→213</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260907.xlsx
+++ b/reports/pdf_rolling5_20260907.xlsx
@@ -2646,23 +2646,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>70560000</v>
+        <v>77616000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.27%</t>
+          <t>2.68%→2.97%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>79→100</t>
+          <t>192→213</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -2690,23 +2690,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>77616000</v>
+        <v>70560000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.97%</t>
+          <t>1.00%→1.27%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>192→213</t>
+          <t>79→100</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260907.xlsx
+++ b/reports/pdf_rolling5_20260907.xlsx
@@ -1849,23 +1849,23 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>로보티즈  (편출)</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2180178000</v>
+        <v>-1322521200</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.00%</t>
+          <t>4.59%→4.34%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>119→106</t>
         </is>
       </c>
     </row>
@@ -1877,23 +1877,23 @@
       <c r="E39" s="17" t="n"/>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>로보티즈  (편출)</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1322521200</v>
+        <v>-2180178000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>4.59%→4.34%</t>
+          <t>0.85%→0.00%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>119→106</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -2646,23 +2646,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>77616000</v>
+        <v>70560000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.68%→2.97%</t>
+          <t>1.00%→1.27%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>192→213</t>
+          <t>79→100</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -2690,23 +2690,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>21</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>70560000</v>
+        <v>77616000</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.27%</t>
+          <t>2.68%→2.97%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>79→100</t>
+          <t>192→213</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
